--- a/database/gazette_database.xlsx
+++ b/database/gazette_database.xlsx
@@ -26,6 +26,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rivers_Groups" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mountains_Entries" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mountains_Groups" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Committees_Entries" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Committees_Groups" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21650,6 +21652,771 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>year_formed</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>chairperson</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>reveal_fact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sarkaria Commission</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>R S Sarkaria</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Centre-state relations</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed how federal power should be distributed, still widely cited in centre-state disputes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Punchhi Commission</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>M M Punchhi</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Centre-state relations</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Revisited Sarkaria-era recommendations decades later amid new federal tensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Mandal Commission</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>B P Mandal</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OBC reservation</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Its recommendations led to 27% OBC reservation being implemented in 1990.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Narasimham Committee</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>M Narasimham</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Banking sector reform</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Laid the groundwork for liberalising India's banking sector in the 1990s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Kelkar Committee</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Vijay Kelkar</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Tax reform</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Proposed direct and indirect tax simplification later reflected in GST-era reforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Shah Commission</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>J C Shah</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Emergency-era excesses</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Investigated abuses of power during the 1975-77 Emergency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Liberhan Commission</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>M S Liberhan</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Babri Masjid demolition</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Took 17 years to submit its report, one of the longest-running inquiry commissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Justice Verma Committee</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>J S Verma</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Criminal law on sexual violence</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Formed after the 2012 Delhi gang-rape case; shaped major criminal law amendments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Malimath Committee</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>V S Malimath</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Criminal justice system reform</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Recommended sweeping changes to India's criminal trial procedures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Vinod Rai Committee</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Vinod Rai</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>BCCI administrative reform</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Formed by the Supreme Court to oversee reforms in Indian cricket administration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Swaminathan Commission</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>M S Swaminathan</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Farmer welfare &amp; MSP</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Its MSP formula recommendation remains a central demand in farmer protests today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Second Administrative Reforms Commission</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Veerappa Moily</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public administration reform</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Produced 15 reports covering everything from e-governance to conflict of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>15th Finance Commission</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>N K Singh</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Centre-state fiscal devolution</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Recommended the formula states use to receive their share of central taxes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Justice Muralidhar Committee</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>S Muralidhar</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Police reform</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>One of several state-level panels examining police accountability mechanisms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Add new rows any time - name must be unique. Leave 'verified' as No until checked against an official source.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>field_name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Centre-state relations</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>polity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OBC reservation</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Banking sector reform</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tax reform</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Emergency-era excesses</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Babri Masjid demolition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>polity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Criminal law on sexual violence</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Criminal justice system reform</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>BCCI administrative reform</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Farmer welfare &amp; MSP</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Public administration reform</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Centre-state fiscal devolution</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Police reform</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Every categorical value used in Entries must have a row here.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
